--- a/data/substitutions.xlsx
+++ b/data/substitutions.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:F3"/>
+  <dimension ref="A1:F6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -478,7 +478,7 @@
         <v>2</v>
       </c>
       <c r="E2" t="n">
-        <v>10</v>
+        <v>7</v>
       </c>
       <c r="F2" t="inlineStr">
         <is>
@@ -507,6 +507,84 @@
         <v>6</v>
       </c>
       <c r="F3" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>10-A</t>
+        </is>
+      </c>
+      <c r="D4" t="n">
+        <v>1</v>
+      </c>
+      <c r="E4" t="n">
+        <v>8</v>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>9-A</t>
+        </is>
+      </c>
+      <c r="D5" t="n">
+        <v>3</v>
+      </c>
+      <c r="E5" t="n">
+        <v>9</v>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>Absent</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>2026-10-12</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>3</v>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>10-B</t>
+        </is>
+      </c>
+      <c r="D6" t="n">
+        <v>3</v>
+      </c>
+      <c r="E6" t="n">
+        <v>9</v>
+      </c>
+      <c r="F6" t="inlineStr">
         <is>
           <t>Absent</t>
         </is>
